--- a/data/trans_dic/Viv_Temp_insuf-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,43; 18,76</t>
+          <t>10,62; 18,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,84; 55,84</t>
+          <t>43,38; 55,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,41; 24,92</t>
+          <t>13,42; 24,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 24,17</t>
+          <t>14,89; 24,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,41; 50,06</t>
+          <t>38,9; 50,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,99; 24,06</t>
+          <t>14,86; 23,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,79; 20,02</t>
+          <t>13,89; 20,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,92; 51,4</t>
+          <t>43,07; 51,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 22,45</t>
+          <t>15,0; 22,16</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,97</t>
+          <t>5,82; 11,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,4; 31,45</t>
+          <t>23,26; 31,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,15</t>
+          <t>7,73; 14,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 11,36</t>
+          <t>6,19; 11,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 26,86</t>
+          <t>19,44; 26,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,61</t>
+          <t>8,88; 13,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,25</t>
+          <t>6,79; 10,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,24; 27,88</t>
+          <t>22,37; 27,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,39</t>
+          <t>9,13; 13,33</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,35</t>
+          <t>0,29; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,72</t>
+          <t>0,87; 3,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,9</t>
+          <t>1,93; 6,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,69</t>
+          <t>0,29; 2,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,36</t>
+          <t>0,26; 2,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,66</t>
+          <t>1,16; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,96</t>
+          <t>0,32; 1,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,4</t>
+          <t>0,68; 2,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,33</t>
+          <t>1,87; 4,2</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,37</t>
+          <t>1,17; 6,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,54</t>
+          <t>2,22; 6,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,6</t>
+          <t>1,59; 7,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,74</t>
+          <t>1,32; 4,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,57</t>
+          <t>2,83; 7,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 48,62</t>
+          <t>3,81; 50,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,31</t>
+          <t>1,65; 4,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,23</t>
+          <t>3,14; 6,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,64; 37,91</t>
+          <t>3,74; 36,17</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,16</t>
+          <t>2,03; 8,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,2</t>
+          <t>0,43; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,25</t>
+          <t>0,09; 2,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 9,61</t>
+          <t>3,22; 9,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,79</t>
+          <t>0,83; 4,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,56</t>
+          <t>3,27; 7,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,32</t>
+          <t>0,87; 3,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,1</t>
+          <t>0,13; 1,09</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,86</t>
+          <t>29,55; 41,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,06</t>
+          <t>0,67; 4,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,93; 40,82</t>
+          <t>28,85; 40,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,87</t>
+          <t>1,08; 3,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,59</t>
+          <t>0,19; 1,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,58; 38,68</t>
+          <t>30,38; 39,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,4</t>
+          <t>1,1; 3,43</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,06</t>
+          <t>0,96; 3,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,87; 23,2</t>
+          <t>16,86; 23,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,06; 37,17</t>
+          <t>28,07; 36,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,11</t>
+          <t>1,45; 3,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,83; 23,08</t>
+          <t>16,71; 23,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,77; 34,31</t>
+          <t>12,66; 34,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,98</t>
+          <t>1,41; 3,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,84; 22,62</t>
+          <t>17,85; 22,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,03; 33,82</t>
+          <t>18,23; 33,81</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,17</t>
+          <t>1,86; 4,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,54</t>
+          <t>0,26; 1,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,19</t>
+          <t>0,64; 3,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,92</t>
+          <t>1,0; 2,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,93</t>
+          <t>0,49; 2,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,66</t>
+          <t>1,65; 3,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,22</t>
+          <t>1,64; 3,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,44</t>
+          <t>0,48; 1,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,93</t>
+          <t>1,29; 3,0</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,89</t>
+          <t>3,46; 4,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14,4; 17,1</t>
+          <t>14,5; 17,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 11,9</t>
+          <t>8,29; 11,96</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,24</t>
+          <t>3,83; 5,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,83</t>
+          <t>13,45; 15,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,92</t>
+          <t>9,65; 16,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 4,89</t>
+          <t>3,83; 4,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,18; 15,97</t>
+          <t>14,21; 16,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,83; 14,88</t>
+          <t>9,7; 14,15</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con temperatura insuficiente</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30729; 55306</t>
+          <t>31297; 55571</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>125834; 164036</t>
+          <t>127434; 162962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41760; 77618</t>
+          <t>41792; 77547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41016; 69415</t>
+          <t>42781; 69441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110902; 144513</t>
+          <t>112301; 145899</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43407; 69672</t>
+          <t>43041; 67128</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>80227; 116527</t>
+          <t>80818; 118675</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249999; 299368</t>
+          <t>250892; 299411</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92007; 134939</t>
+          <t>90161; 133184</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28641; 55434</t>
+          <t>29426; 57164</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117588; 158070</t>
+          <t>116879; 156324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40595; 78546</t>
+          <t>40053; 75469</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32698; 59502</t>
+          <t>32442; 61087</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100627; 140486</t>
+          <t>101698; 139940</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45277; 70082</t>
+          <t>45714; 69841</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67840; 105491</t>
+          <t>69916; 107272</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>228066; 285966</t>
+          <t>229487; 284834</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93685; 138316</t>
+          <t>94371; 137696</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>940; 7601</t>
+          <t>935; 7775</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2740; 11855</t>
+          <t>2756; 12629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5705; 18640</t>
+          <t>6096; 19845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>982; 9157</t>
+          <t>984; 8335</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>894; 7944</t>
+          <t>884; 8587</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4045; 12765</t>
+          <t>4041; 12860</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2844; 13059</t>
+          <t>2128; 12246</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4641; 15745</t>
+          <t>4426; 15659</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12232; 28798</t>
+          <t>12427; 27968</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4157; 20101</t>
+          <t>4390; 22515</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8595; 24196</t>
+          <t>8225; 23492</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4827; 23754</t>
+          <t>4959; 23930</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5110; 18455</t>
+          <t>5134; 18550</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11749; 29336</t>
+          <t>10960; 29391</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16859; 231271</t>
+          <t>18129; 241992</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11762; 32920</t>
+          <t>12579; 33114</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24107; 47176</t>
+          <t>23782; 49334</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28723; 298810</t>
+          <t>29481; 285142</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5094; 17350</t>
+          <t>4326; 17679</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>935; 8866</t>
+          <t>918; 7855</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161; 4029</t>
+          <t>163; 3880</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7053; 21101</t>
+          <t>7081; 20490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1765; 10476</t>
+          <t>1814; 10375</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2596</t>
+          <t>0; 3114</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13978; 32657</t>
+          <t>14154; 32562</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3651; 14262</t>
+          <t>3744; 14576</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>562; 4792</t>
+          <t>567; 4754</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5899</t>
+          <t>0; 5937</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>76123; 107524</t>
+          <t>77758; 108592</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1867; 10958</t>
+          <t>1801; 11628</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7277</t>
+          <t>0; 7091</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>79025; 111497</t>
+          <t>78791; 109750</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2637; 9948</t>
+          <t>2765; 9959</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>973; 8833</t>
+          <t>1079; 9783</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>163988; 207409</t>
+          <t>162893; 209508</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6047; 17890</t>
+          <t>5816; 18090</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6259; 20284</t>
+          <t>6359; 19975</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110782; 152325</t>
+          <t>110703; 155464</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>175162; 232030</t>
+          <t>175241; 228634</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10577; 28512</t>
+          <t>10077; 27060</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>116336; 159569</t>
+          <t>115490; 161868</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>116932; 291404</t>
+          <t>107493; 291296</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18072; 40457</t>
+          <t>19185; 41516</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>240423; 304923</t>
+          <t>240568; 300333</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>265645; 498367</t>
+          <t>268562; 498272</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>14610; 32515</t>
+          <t>14512; 33213</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2039; 11977</t>
+          <t>2051; 12726</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6474; 29672</t>
+          <t>5942; 29728</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8245; 24088</t>
+          <t>8239; 23457</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4123; 15985</t>
+          <t>4013; 16990</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11636; 26302</t>
+          <t>11807; 27242</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25767; 51564</t>
+          <t>26262; 51386</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7487; 23084</t>
+          <t>7699; 23749</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19842; 48229</t>
+          <t>21303; 49470</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>120094; 167483</t>
+          <t>118571; 167116</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>488903; 580562</t>
+          <t>492038; 577072</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>281962; 411882</t>
+          <t>286686; 413730</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>135657; 186311</t>
+          <t>136385; 187873</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>473334; 561205</t>
+          <t>476803; 562513</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>360218; 665407</t>
+          <t>358228; 630368</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>270685; 341272</t>
+          <t>267675; 337458</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>984256; 1108322</t>
+          <t>986040; 1118529</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>705061; 1067406</t>
+          <t>695414; 1014653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Viv_Temp_insuf-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Viv_Temp_insuf-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,39; 30,03</t>
+          <t>9,71; 17,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18,27; 26,13</t>
+          <t>11,32; 18,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,28; 26,67</t>
+          <t>11,18; 16,3</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 14,89</t>
+          <t>12,69; 20,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 12,59</t>
+          <t>18,57; 25,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 13,45</t>
+          <t>16,56; 21,47</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,55</t>
+          <t>20,17; 29,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,55</t>
+          <t>20,53; 27,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,18</t>
+          <t>21,63; 27,11</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,35</t>
+          <t>24,93; 37,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,48</t>
+          <t>27,68; 36,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 7,06</t>
+          <t>27,61; 34,59</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,86</t>
+          <t>28,09; 39,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>19,01; 27,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,93</t>
+          <t>24,55; 31,4</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,27</t>
+          <t>14,47; 23,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,9</t>
+          <t>9,93; 16,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,36</t>
+          <t>13,46; 18,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,48; 37,6</t>
+          <t>28,61; 36,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,49; 38,18</t>
+          <t>38,58; 45,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,48; 36,63</t>
+          <t>35,17; 40,66</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,6</t>
+          <t>83,32; 88,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,45</t>
+          <t>86,8; 90,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,6</t>
+          <t>86,0; 89,27</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,04; 13,64</t>
+          <t>36,8; 40,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,17</t>
+          <t>39,47; 42,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,46; 13,01</t>
+          <t>38,64; 40,93</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 100,0%)</t>
+          <t>Población con temperatura insuficiente, en verano o en invierno, en la vivienda (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1088,17 +1088,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78378</t>
+          <t>41763</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>68293</t>
+          <t>44587</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146671</t>
+          <t>86350</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>61814; 95759</t>
+          <t>30947; 54498</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57757; 82590</t>
+          <t>35791; 56935</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128780; 169340</t>
+          <t>70988; 103485</t>
         </is>
       </c>
     </row>
@@ -1161,17 +1161,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>154</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>217</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>58667</t>
+          <t>87672</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56708</t>
+          <t>117556</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>115375</t>
+          <t>205229</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42343; 79018</t>
+          <t>67363; 109540</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44953; 68816</t>
+          <t>101497; 137175</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>98114; 144868</t>
+          <t>178426; 231283</t>
         </is>
       </c>
     </row>
@@ -1234,17 +1234,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>77052</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>86087</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>163138</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7907; 23842</t>
+          <t>63733; 92687</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5810; 16209</t>
+          <t>73178; 99473</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15895; 34828</t>
+          <t>145466; 182295</t>
         </is>
       </c>
     </row>
@@ -1307,17 +1307,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>107</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>186</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>293</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>112649</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>22463</t>
+          <t>132748</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38243</t>
+          <t>245396</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8018; 31175</t>
+          <t>93014; 138231</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14284; 35786</t>
+          <t>116518; 153097</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26186; 56156</t>
+          <t>219270; 274702</t>
         </is>
       </c>
     </row>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>68368</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>51467</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>119835</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>746; 7931</t>
+          <t>57358; 81631</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3051</t>
+          <t>43517; 63140</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1460; 8372</t>
+          <t>106310; 136004</t>
         </is>
       </c>
     </row>
@@ -1453,17 +1453,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>132</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>49733</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>34390</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>84124</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2219; 11550</t>
+          <t>39045; 62190</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2816; 10298</t>
+          <t>26189; 43807</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6221; 17961</t>
+          <t>71842; 100000</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>413</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>612</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>240246</t>
+          <t>236248</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>267239</t>
+          <t>323756</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>507485</t>
+          <t>560004</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>212190; 270606</t>
+          <t>204778; 261682</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>243154; 294738</t>
+          <t>297050; 350157</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>469558; 546492</t>
+          <t>522446; 604113</t>
         </is>
       </c>
     </row>
@@ -1599,17 +1599,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>662</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>939</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>1601</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>18719</t>
+          <t>689402</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25017</t>
+          <t>738485</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>43737</t>
+          <t>1427886</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10483; 28760</t>
+          <t>664982; 708991</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16567; 36987</t>
+          <t>721574; 752903</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31032; 58717</t>
+          <t>1401209; 1454576</t>
         </is>
       </c>
     </row>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>3389</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>434277</t>
+          <t>1362887</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>456129</t>
+          <t>1529076</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>890406</t>
+          <t>2891963</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>390005; 481850</t>
+          <t>1297904; 1432729</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>418692; 492341</t>
+          <t>1473565; 1583441</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>833004; 945539</t>
+          <t>2805564; 2971348</t>
         </is>
       </c>
     </row>
